--- a/Test2_Solved.xlsx
+++ b/Test2_Solved.xlsx
@@ -202,14 +202,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;#   &quot;@&quot;  #&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;Mr.  &quot;@"/>
     <numFmt numFmtId="168" formatCode="&quot;Shri &quot;@"/>
+    <numFmt numFmtId="171" formatCode="&quot;Mr.  &quot;@&quot; $&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +278,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -309,12 +319,6 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF66CC"/>
         <bgColor indexed="64"/>
@@ -324,6 +328,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF0070C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -370,7 +379,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -396,54 +405,45 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="@\ &quot;$&quot;"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <b/>
@@ -761,7 +761,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -777,7 +777,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -788,20 +788,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="4" spans="4:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D4" s="1" t="s">
@@ -839,23 +839,28 @@
       <c r="E5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>42</v>
       </c>
       <c r="I5" s="3">
         <v>36333</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="17">
+      <c r="J5" s="11">
+        <v>66000</v>
+      </c>
+      <c r="K5" s="12">
         <v>10000</v>
       </c>
-      <c r="L5" s="16"/>
+      <c r="L5" s="11">
+        <f>J5-K5</f>
+        <v>56000</v>
+      </c>
     </row>
     <row r="6" spans="4:12" ht="18" x14ac:dyDescent="0.25">
       <c r="D6" s="4">
@@ -864,23 +869,28 @@
       <c r="E6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="16" t="s">
         <v>43</v>
       </c>
       <c r="I6" s="3">
         <v>36636</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16">
+      <c r="J6" s="11">
+        <v>70000</v>
+      </c>
+      <c r="K6" s="11">
         <v>11000</v>
       </c>
-      <c r="L6" s="16"/>
+      <c r="L6" s="11">
+        <f>J6-K6</f>
+        <v>59000</v>
+      </c>
     </row>
     <row r="7" spans="4:12" ht="18" x14ac:dyDescent="0.25">
       <c r="D7" s="4">
@@ -889,25 +899,25 @@
       <c r="E7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="16" t="s">
         <v>44</v>
       </c>
       <c r="I7" s="5">
         <v>36011</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="11">
         <v>75000</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="12">
         <v>40000</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="11">
         <f>J7-K7</f>
         <v>35000</v>
       </c>
@@ -919,25 +929,25 @@
       <c r="E8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="16" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="3">
         <v>37123</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="11">
         <v>84000</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="12">
         <v>35000</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="11">
         <f>J8-K8</f>
         <v>49000</v>
       </c>
@@ -949,23 +959,28 @@
       <c r="E9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="16" t="s">
         <v>42</v>
       </c>
       <c r="I9" s="3">
         <v>37143</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17">
+      <c r="J9" s="11">
+        <v>80000</v>
+      </c>
+      <c r="K9" s="12">
         <v>9000</v>
       </c>
-      <c r="L9" s="16"/>
+      <c r="L9" s="11">
+        <f>J9-K9</f>
+        <v>71000</v>
+      </c>
     </row>
     <row r="10" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D10" s="4">
@@ -974,25 +989,25 @@
       <c r="E10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="16" t="s">
         <v>45</v>
       </c>
       <c r="I10" s="3">
         <v>37839</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="11">
         <v>36000</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="11">
         <v>12000</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="13">
         <f>J10-K10</f>
         <v>24000</v>
       </c>
@@ -1004,52 +1019,52 @@
       <c r="E11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="16" t="s">
         <v>42</v>
       </c>
       <c r="I11" s="3">
         <v>35496</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="11">
         <v>45000</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="11">
         <v>15000</v>
       </c>
-      <c r="L11" s="18">
-        <f t="shared" ref="L11:L13" si="0">J11-K11</f>
+      <c r="L11" s="13">
+        <f t="shared" ref="L11:L14" si="0">J11-K11</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="12" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:12" ht="18" x14ac:dyDescent="0.35">
       <c r="D12" s="4">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>27</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="16" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="3">
         <v>33789</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="11">
         <v>45500</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="11">
         <v>13000</v>
       </c>
       <c r="L12" s="18">
@@ -1057,87 +1072,92 @@
         <v>32500</v>
       </c>
     </row>
-    <row r="13" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:12" ht="18" x14ac:dyDescent="0.25">
       <c r="D13" s="4">
         <v>7</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="5">
         <v>36784</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="11">
         <v>55500</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="12">
         <v>20000</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="13">
         <f t="shared" si="0"/>
         <v>35500</v>
       </c>
     </row>
-    <row r="14" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:12" ht="18" x14ac:dyDescent="0.35">
       <c r="D14" s="4">
         <v>6</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="16" t="s">
         <v>42</v>
       </c>
       <c r="I14" s="3">
         <v>34884</v>
       </c>
-      <c r="J14" s="16"/>
+      <c r="J14" s="11">
+        <v>90000</v>
+      </c>
       <c r="K14" s="17">
         <v>8500</v>
       </c>
-      <c r="L14" s="16"/>
+      <c r="L14" s="11">
+        <f t="shared" si="0"/>
+        <v>81500</v>
+      </c>
     </row>
     <row r="15" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D15" s="4">
         <v>5</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="16" t="s">
         <v>48</v>
       </c>
       <c r="I15" s="3">
         <v>38029</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="11">
         <v>75000</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="12">
         <v>40000</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="11">
         <f>J15-K15</f>
         <v>35000</v>
       </c>
@@ -1146,28 +1166,28 @@
       <c r="D16" s="4">
         <v>4</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>31</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="16" t="s">
         <v>47</v>
       </c>
       <c r="I16" s="3">
         <v>36506</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="11">
         <v>75000</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="12">
         <v>39000</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="11">
         <f>J16-K16</f>
         <v>36000</v>
       </c>
@@ -1179,50 +1199,56 @@
       <c r="E17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>32</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="16" t="s">
         <v>49</v>
       </c>
       <c r="I17" s="3">
         <v>35254</v>
       </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="17">
+      <c r="J17" s="11">
+        <v>95000</v>
+      </c>
+      <c r="K17" s="12">
         <v>8699</v>
       </c>
-      <c r="L17" s="16"/>
+      <c r="L17" s="11">
+        <f>J17-K17</f>
+        <v>86301</v>
+      </c>
     </row>
     <row r="18" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="16" t="s">
         <v>42</v>
       </c>
       <c r="I18" s="3">
         <v>36658</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="11">
         <v>36000</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="11">
         <v>12000</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="11">
+        <f t="shared" ref="L18:L19" si="1">J18-K18</f>
         <v>24000</v>
       </c>
     </row>
@@ -1233,23 +1259,28 @@
       <c r="E19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="16" t="s">
         <v>50</v>
       </c>
       <c r="I19" s="3">
         <v>39065</v>
       </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17">
+      <c r="J19" s="11">
+        <v>11000</v>
+      </c>
+      <c r="K19" s="12">
         <v>7800</v>
       </c>
-      <c r="L19" s="16"/>
+      <c r="L19" s="11">
+        <f t="shared" si="1"/>
+        <v>3200</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="D5:D19">
@@ -1259,7 +1290,7 @@
     <mergeCell ref="F1:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E19">
-    <cfRule type="endsWith" dxfId="2" priority="4" operator="endsWith" text="h">
+    <cfRule type="endsWith" dxfId="0" priority="4" operator="endsWith" text="h">
       <formula>RIGHT(E9,LEN("h"))="h"</formula>
     </cfRule>
   </conditionalFormatting>
